--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.116.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.116.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.116.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.116.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.116.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.116.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0116.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0116.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -610,11 +610,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: specifying therein the dates and general description of theâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L23: symbol-only separator/garbage line :: (29).</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -630,7 +634,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L112: line starts with digit/letter garbage token | suspicious token(s): 8Decrees (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Decrees 3" vs "8Decrees 4" :: 8Decrees.</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pleading</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ pleading</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pleading</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -691,7 +695,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • is to be</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -724,7 +732,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ is to be</t>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • is to be</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -742,7 +750,11 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • of this</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -763,7 +775,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -775,7 +787,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ of this</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • of this</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -793,7 +805,11 @@
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L112: line starts with digit/letter garbage token | suspicious token(s): 8Decrees (letter/digit mix) | localized OCR phrase divergence vs other OCR: "Decrees 3" vs "8Decrees 4" :: 8Decrees.</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -1025,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1142,7 +1158,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
